--- a/Hasan Panwar/GBPS Hasan Panwar.xlsx
+++ b/Hasan Panwar/GBPS Hasan Panwar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Hasan Panwar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82692B7D-FBA2-48D7-BFEB-8D4940633E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C55BFB-311D-498E-B5EB-B67986182130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="443">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -526,9 +526,6 @@
     <t>0340-2837694</t>
   </si>
   <si>
-    <t>Usman Jamali</t>
-  </si>
-  <si>
     <t>Jamal Uddin Pitafi</t>
   </si>
   <si>
@@ -1133,6 +1130,240 @@
   </si>
   <si>
     <t>0370-2162545</t>
+  </si>
+  <si>
+    <t>Hasnain Abbas</t>
+  </si>
+  <si>
+    <t>Bahadur Ali</t>
+  </si>
+  <si>
+    <t>43102-9526249-3</t>
+  </si>
+  <si>
+    <t>0308-2783346</t>
+  </si>
+  <si>
+    <t>Muhammad Shayan</t>
+  </si>
+  <si>
+    <t>Ajwa</t>
+  </si>
+  <si>
+    <t>Zubair Ali</t>
+  </si>
+  <si>
+    <t>43407-0410728-5</t>
+  </si>
+  <si>
+    <t>0304-2564988</t>
+  </si>
+  <si>
+    <t>Areeba</t>
+  </si>
+  <si>
+    <t>Bibi Kubra</t>
+  </si>
+  <si>
+    <t>Fazal Ur Rehman</t>
+  </si>
+  <si>
+    <t>43503-0411227-9</t>
+  </si>
+  <si>
+    <t>0308-3115759</t>
+  </si>
+  <si>
+    <t>Abdul Rehman</t>
+  </si>
+  <si>
+    <t>Naveed Ali</t>
+  </si>
+  <si>
+    <t>Wazir Ali</t>
+  </si>
+  <si>
+    <t>43301-6977615-7</t>
+  </si>
+  <si>
+    <t>0302-2678500</t>
+  </si>
+  <si>
+    <t>Ghulam Akbar</t>
+  </si>
+  <si>
+    <t>Nazeer Ahmed</t>
+  </si>
+  <si>
+    <t>43301-6976665-7</t>
+  </si>
+  <si>
+    <t>0308-1177354</t>
+  </si>
+  <si>
+    <t>Atif</t>
+  </si>
+  <si>
+    <t>Nangar</t>
+  </si>
+  <si>
+    <t>43302-8079055-3</t>
+  </si>
+  <si>
+    <t>0302-2756166</t>
+  </si>
+  <si>
+    <t>Shabrooz</t>
+  </si>
+  <si>
+    <t>Amir Ali</t>
+  </si>
+  <si>
+    <t>43304-2882502-9</t>
+  </si>
+  <si>
+    <t>0305-2113805</t>
+  </si>
+  <si>
+    <t>Usman Ali</t>
+  </si>
+  <si>
+    <t>Nazima</t>
+  </si>
+  <si>
+    <t>Wazir Ahmed</t>
+  </si>
+  <si>
+    <t>Shehzad Ali</t>
+  </si>
+  <si>
+    <t>Irshad Ali</t>
+  </si>
+  <si>
+    <t>43407-0404237-3</t>
+  </si>
+  <si>
+    <t>0307-8251995</t>
+  </si>
+  <si>
+    <t>Mahira Khatoon</t>
+  </si>
+  <si>
+    <t>Shahnawaz Khan</t>
+  </si>
+  <si>
+    <t>Iman Batool</t>
+  </si>
+  <si>
+    <t>Altaf Ali</t>
+  </si>
+  <si>
+    <t>43304-4336625-1</t>
+  </si>
+  <si>
+    <t>0305-2998984</t>
+  </si>
+  <si>
+    <t>Nosheen</t>
+  </si>
+  <si>
+    <t>Ali Raza</t>
+  </si>
+  <si>
+    <t>Munawar Ali</t>
+  </si>
+  <si>
+    <t>42201-1441041-1</t>
+  </si>
+  <si>
+    <t>0300-3659733</t>
+  </si>
+  <si>
+    <t>Farhana</t>
+  </si>
+  <si>
+    <t>Shokat Ali</t>
+  </si>
+  <si>
+    <t>43407-0394504-1</t>
+  </si>
+  <si>
+    <t>0309-2886685</t>
+  </si>
+  <si>
+    <t>Hasan Raza</t>
+  </si>
+  <si>
+    <t>Zameer Ahmed</t>
+  </si>
+  <si>
+    <t>45204-8402255-7</t>
+  </si>
+  <si>
+    <t>0305-3958068</t>
+  </si>
+  <si>
+    <t>Ghulam Zahra</t>
+  </si>
+  <si>
+    <t>Shafaq Abul Shakoor</t>
+  </si>
+  <si>
+    <t>Abdul Shakoor</t>
+  </si>
+  <si>
+    <t>42501-2966499-7</t>
+  </si>
+  <si>
+    <t>0316-2561514</t>
+  </si>
+  <si>
+    <t>Sehar</t>
+  </si>
+  <si>
+    <t>Muhammad Aqib</t>
+  </si>
+  <si>
+    <t>Imran Ali</t>
+  </si>
+  <si>
+    <t>42501-5441828-7</t>
+  </si>
+  <si>
+    <t>0322-2325049</t>
+  </si>
+  <si>
+    <t>Muzammil Ali</t>
+  </si>
+  <si>
+    <t>Ali Khan</t>
+  </si>
+  <si>
+    <t>43304-4878511-7</t>
+  </si>
+  <si>
+    <t>0306-2097696</t>
+  </si>
+  <si>
+    <t>Naheed</t>
+  </si>
+  <si>
+    <t>45205-1103235-5</t>
+  </si>
+  <si>
+    <t>0306-0070356</t>
+  </si>
+  <si>
+    <t>Usman Jamal</t>
+  </si>
+  <si>
+    <t>0325-8166670</t>
+  </si>
+  <si>
+    <t>0312-2462671</t>
+  </si>
+  <si>
+    <t>0312-2462617</t>
   </si>
 </sst>
 </file>
@@ -3208,7 +3439,9 @@
       <c r="L29" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="M29" s="10"/>
+      <c r="M29" s="10" t="s">
+        <v>442</v>
+      </c>
       <c r="N29" s="8"/>
       <c r="O29" s="10" t="s">
         <v>29</v>
@@ -3701,7 +3934,9 @@
       <c r="L40" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="M40" s="10"/>
+      <c r="M40" s="10" t="s">
+        <v>441</v>
+      </c>
       <c r="N40" s="8"/>
       <c r="O40" s="10" t="s">
         <v>29</v>
@@ -4033,10 +4268,10 @@
         <v>1801</v>
       </c>
       <c r="D48" s="18" t="s">
+        <v>439</v>
+      </c>
+      <c r="E48" s="19" t="s">
         <v>163</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>164</v>
       </c>
       <c r="F48" s="10" t="s">
         <v>18</v>
@@ -4057,9 +4292,11 @@
         <v>45523</v>
       </c>
       <c r="L48" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="M48" s="10"/>
+        <v>164</v>
+      </c>
+      <c r="M48" s="10" t="s">
+        <v>440</v>
+      </c>
       <c r="N48" s="8"/>
       <c r="O48" s="10" t="s">
         <v>24</v>
@@ -4076,7 +4313,7 @@
         <v>1802</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E49" s="20" t="s">
         <v>156</v>
@@ -4103,7 +4340,7 @@
         <v>157</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N49" s="8"/>
       <c r="O49" s="10" t="s">
@@ -4121,10 +4358,10 @@
         <v>1803</v>
       </c>
       <c r="D50" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="E50" s="20" t="s">
         <v>168</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>169</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>18</v>
@@ -4145,10 +4382,10 @@
         <v>45523</v>
       </c>
       <c r="L50" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="M50" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="M50" s="10" t="s">
-        <v>171</v>
       </c>
       <c r="N50" s="8"/>
       <c r="O50" s="10" t="s">
@@ -4169,7 +4406,7 @@
         <v>51</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>18</v>
@@ -4190,10 +4427,10 @@
         <v>45523</v>
       </c>
       <c r="L51" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="M51" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="M51" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="N51" s="8"/>
       <c r="O51" s="10" t="s">
@@ -4211,10 +4448,10 @@
         <v>1805</v>
       </c>
       <c r="D52" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="E52" s="22" t="s">
         <v>175</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>176</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>18</v>
@@ -4235,10 +4472,10 @@
         <v>45523</v>
       </c>
       <c r="L52" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="M52" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="M52" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="N52" s="10"/>
       <c r="O52" s="10" t="s">
@@ -4256,10 +4493,10 @@
         <v>1806</v>
       </c>
       <c r="D53" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="E53" s="24" t="s">
         <v>179</v>
-      </c>
-      <c r="E53" s="24" t="s">
-        <v>180</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>18</v>
@@ -4280,10 +4517,10 @@
         <v>45523</v>
       </c>
       <c r="L53" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="M53" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="M53" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="N53" s="10"/>
       <c r="O53" s="10" t="s">
@@ -4301,10 +4538,10 @@
         <v>1807</v>
       </c>
       <c r="D54" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E54" s="24" t="s">
         <v>181</v>
-      </c>
-      <c r="E54" s="24" t="s">
-        <v>182</v>
       </c>
       <c r="F54" s="10" t="s">
         <v>18</v>
@@ -4325,10 +4562,10 @@
         <v>45523</v>
       </c>
       <c r="L54" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="M54" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="M54" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="N54" s="10"/>
       <c r="O54" s="10" t="s">
@@ -4346,10 +4583,10 @@
         <v>1808</v>
       </c>
       <c r="D55" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="E55" s="24" t="s">
         <v>185</v>
-      </c>
-      <c r="E55" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>18</v>
@@ -4370,10 +4607,10 @@
         <v>45523</v>
       </c>
       <c r="L55" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="M55" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="M55" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="N55" s="10"/>
       <c r="O55" s="10" t="s">
@@ -4391,10 +4628,10 @@
         <v>1809</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F56" s="10" t="s">
         <v>18</v>
@@ -4415,10 +4652,10 @@
         <v>45523</v>
       </c>
       <c r="L56" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="M56" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="M56" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="N56" s="10"/>
       <c r="O56" s="10" t="s">
@@ -4436,10 +4673,10 @@
         <v>1810</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>18</v>
@@ -4460,10 +4697,10 @@
         <v>45523</v>
       </c>
       <c r="L57" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="M57" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="M57" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="N57" s="10"/>
       <c r="O57" s="10" t="s">
@@ -4481,10 +4718,10 @@
         <v>1811</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F58" s="10" t="s">
         <v>18</v>
@@ -4505,10 +4742,10 @@
         <v>45523</v>
       </c>
       <c r="L58" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="M58" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="M58" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="N58" s="10"/>
       <c r="O58" s="10" t="s">
@@ -4526,10 +4763,10 @@
         <v>1812</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>18</v>
@@ -4550,10 +4787,10 @@
         <v>45523</v>
       </c>
       <c r="L59" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="M59" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="M59" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="N59" s="10"/>
       <c r="O59" s="10" t="s">
@@ -4571,10 +4808,10 @@
         <v>1813</v>
       </c>
       <c r="D60" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="E60" s="24" t="s">
         <v>193</v>
-      </c>
-      <c r="E60" s="24" t="s">
-        <v>194</v>
       </c>
       <c r="F60" s="10" t="s">
         <v>106</v>
@@ -4595,7 +4832,7 @@
         <v>45523</v>
       </c>
       <c r="L60" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M60" s="10" t="s">
         <v>148</v>
@@ -4616,10 +4853,10 @@
         <v>1814</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>106</v>
@@ -4640,10 +4877,10 @@
         <v>45523</v>
       </c>
       <c r="L61" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="M61" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="M61" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="N61" s="10"/>
       <c r="O61" s="10" t="s">
@@ -4661,10 +4898,10 @@
         <v>1815</v>
       </c>
       <c r="D62" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="E62" s="24" t="s">
         <v>197</v>
-      </c>
-      <c r="E62" s="24" t="s">
-        <v>198</v>
       </c>
       <c r="F62" s="10" t="s">
         <v>106</v>
@@ -4685,10 +4922,10 @@
         <v>45523</v>
       </c>
       <c r="L62" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="M62" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="M62" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="N62" s="10"/>
       <c r="O62" s="10" t="s">
@@ -4706,7 +4943,7 @@
         <v>1816</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E63" s="24" t="s">
         <v>160</v>
@@ -4751,10 +4988,10 @@
         <v>1817</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F64" s="10" t="s">
         <v>106</v>
@@ -4775,10 +5012,10 @@
         <v>45523</v>
       </c>
       <c r="L64" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="M64" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="M64" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="N64" s="10"/>
       <c r="O64" s="10" t="s">
@@ -4799,7 +5036,7 @@
         <v>76</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>18</v>
@@ -4820,10 +5057,10 @@
         <v>45525</v>
       </c>
       <c r="L65" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="M65" s="10" t="s">
         <v>204</v>
-      </c>
-      <c r="M65" s="10" t="s">
-        <v>205</v>
       </c>
       <c r="N65" s="10"/>
       <c r="O65" s="10" t="s">
@@ -4841,10 +5078,10 @@
         <v>1819</v>
       </c>
       <c r="D66" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="E66" s="24" t="s">
         <v>206</v>
-      </c>
-      <c r="E66" s="24" t="s">
-        <v>207</v>
       </c>
       <c r="F66" s="10" t="s">
         <v>18</v>
@@ -4865,10 +5102,10 @@
         <v>45525</v>
       </c>
       <c r="L66" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="M66" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="M66" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="N66" s="10"/>
       <c r="O66" s="10" t="s">
@@ -4886,7 +5123,7 @@
         <v>1820</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E67" s="24" t="s">
         <v>123</v>
@@ -4910,10 +5147,10 @@
         <v>45525</v>
       </c>
       <c r="L67" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="M67" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="M67" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="N67" s="10"/>
       <c r="O67" s="10" t="s">
@@ -4931,7 +5168,7 @@
         <v>1821</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E68" s="24" t="s">
         <v>123</v>
@@ -4955,10 +5192,10 @@
         <v>45525</v>
       </c>
       <c r="L68" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="M68" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="M68" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="N68" s="10"/>
       <c r="O68" s="10" t="s">
@@ -4976,10 +5213,10 @@
         <v>1822</v>
       </c>
       <c r="D69" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E69" s="24" t="s">
         <v>214</v>
-      </c>
-      <c r="E69" s="24" t="s">
-        <v>215</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>18</v>
@@ -5000,10 +5237,10 @@
         <v>45525</v>
       </c>
       <c r="L69" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="M69" s="10" t="s">
         <v>216</v>
-      </c>
-      <c r="M69" s="10" t="s">
-        <v>217</v>
       </c>
       <c r="N69" s="10"/>
       <c r="O69" s="10" t="s">
@@ -5021,10 +5258,10 @@
         <v>1823</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F70" s="10" t="s">
         <v>106</v>
@@ -5045,10 +5282,10 @@
         <v>45525</v>
       </c>
       <c r="L70" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="M70" s="10" t="s">
         <v>216</v>
-      </c>
-      <c r="M70" s="10" t="s">
-        <v>217</v>
       </c>
       <c r="N70" s="10"/>
       <c r="O70" s="10" t="s">
@@ -5066,7 +5303,7 @@
         <v>1824</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E71" s="24" t="s">
         <v>38</v>
@@ -5090,10 +5327,10 @@
         <v>45526</v>
       </c>
       <c r="L71" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="M71" s="10" t="s">
         <v>220</v>
-      </c>
-      <c r="M71" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="N71" s="10"/>
       <c r="O71" s="10" t="s">
@@ -5111,10 +5348,10 @@
         <v>1825</v>
       </c>
       <c r="D72" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="E72" s="24" t="s">
         <v>222</v>
-      </c>
-      <c r="E72" s="24" t="s">
-        <v>223</v>
       </c>
       <c r="F72" s="10" t="s">
         <v>18</v>
@@ -5135,10 +5372,10 @@
         <v>45526</v>
       </c>
       <c r="L72" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="M72" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="M72" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="N72" s="10"/>
       <c r="O72" s="10" t="s">
@@ -5156,10 +5393,10 @@
         <v>1826</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E73" s="24" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>18</v>
@@ -5180,10 +5417,10 @@
         <v>45526</v>
       </c>
       <c r="L73" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="M73" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="M73" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="N73" s="10"/>
       <c r="O73" s="10" t="s">
@@ -5201,10 +5438,10 @@
         <v>1827</v>
       </c>
       <c r="D74" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="E74" s="24" t="s">
         <v>227</v>
-      </c>
-      <c r="E74" s="24" t="s">
-        <v>228</v>
       </c>
       <c r="F74" s="10" t="s">
         <v>18</v>
@@ -5225,10 +5462,10 @@
         <v>45527</v>
       </c>
       <c r="L74" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="M74" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="M74" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="N74" s="10"/>
       <c r="O74" s="10" t="s">
@@ -5246,10 +5483,10 @@
         <v>1828</v>
       </c>
       <c r="D75" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="E75" s="24" t="s">
         <v>231</v>
-      </c>
-      <c r="E75" s="24" t="s">
-        <v>232</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>18</v>
@@ -5270,10 +5507,10 @@
         <v>45527</v>
       </c>
       <c r="L75" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="M75" s="27" t="s">
         <v>233</v>
-      </c>
-      <c r="M75" s="27" t="s">
-        <v>234</v>
       </c>
       <c r="N75" s="10"/>
       <c r="O75" s="10" t="s">
@@ -5291,10 +5528,10 @@
         <v>1829</v>
       </c>
       <c r="D76" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="E76" s="24" t="s">
         <v>235</v>
-      </c>
-      <c r="E76" s="24" t="s">
-        <v>236</v>
       </c>
       <c r="F76" s="10" t="s">
         <v>106</v>
@@ -5315,10 +5552,10 @@
         <v>45528</v>
       </c>
       <c r="L76" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="M76" s="10" t="s">
         <v>237</v>
-      </c>
-      <c r="M76" s="10" t="s">
-        <v>238</v>
       </c>
       <c r="N76" s="10"/>
       <c r="O76" s="10" t="s">
@@ -5336,7 +5573,7 @@
         <v>1830</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E77" s="24" t="s">
         <v>150</v>
@@ -5381,10 +5618,10 @@
         <v>1831</v>
       </c>
       <c r="D78" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="E78" s="24" t="s">
         <v>240</v>
-      </c>
-      <c r="E78" s="24" t="s">
-        <v>241</v>
       </c>
       <c r="F78" s="10" t="s">
         <v>106</v>
@@ -5405,10 +5642,10 @@
         <v>45531</v>
       </c>
       <c r="L78" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="M78" s="10" t="s">
         <v>242</v>
-      </c>
-      <c r="M78" s="10" t="s">
-        <v>243</v>
       </c>
       <c r="N78" s="10"/>
       <c r="O78" s="10" t="s">
@@ -5426,10 +5663,10 @@
         <v>1832</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E79" s="24" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>106</v>
@@ -5450,10 +5687,10 @@
         <v>45531</v>
       </c>
       <c r="L79" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="M79" s="10" t="s">
         <v>204</v>
-      </c>
-      <c r="M79" s="10" t="s">
-        <v>205</v>
       </c>
       <c r="N79" s="10"/>
       <c r="O79" s="10" t="s">
@@ -5471,10 +5708,10 @@
         <v>1833</v>
       </c>
       <c r="D80" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="E80" s="24" t="s">
         <v>245</v>
-      </c>
-      <c r="E80" s="24" t="s">
-        <v>246</v>
       </c>
       <c r="F80" s="10" t="s">
         <v>106</v>
@@ -5495,10 +5732,10 @@
         <v>45531</v>
       </c>
       <c r="L80" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="M80" s="10" t="s">
         <v>247</v>
-      </c>
-      <c r="M80" s="10" t="s">
-        <v>248</v>
       </c>
       <c r="N80" s="10"/>
       <c r="O80" s="10" t="s">
@@ -5516,10 +5753,10 @@
         <v>1834</v>
       </c>
       <c r="D81" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="E81" s="24" t="s">
         <v>249</v>
-      </c>
-      <c r="E81" s="24" t="s">
-        <v>250</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>18</v>
@@ -5540,10 +5777,10 @@
         <v>45531</v>
       </c>
       <c r="L81" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="M81" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="M81" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="N81" s="10"/>
       <c r="O81" s="10" t="s">
@@ -5561,10 +5798,10 @@
         <v>1835</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E82" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F82" s="10" t="s">
         <v>106</v>
@@ -5585,10 +5822,10 @@
         <v>45531</v>
       </c>
       <c r="L82" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="M82" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="M82" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="N82" s="10"/>
       <c r="O82" s="10" t="s">
@@ -5606,10 +5843,10 @@
         <v>1836</v>
       </c>
       <c r="D83" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="E83" s="24" t="s">
         <v>254</v>
-      </c>
-      <c r="E83" s="24" t="s">
-        <v>255</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>18</v>
@@ -5630,10 +5867,10 @@
         <v>45532</v>
       </c>
       <c r="L83" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="M83" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="M83" s="10" t="s">
-        <v>257</v>
       </c>
       <c r="N83" s="10"/>
       <c r="O83" s="10" t="s">
@@ -5651,10 +5888,10 @@
         <v>1837</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E84" s="24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F84" s="10" t="s">
         <v>18</v>
@@ -5675,10 +5912,10 @@
         <v>45532</v>
       </c>
       <c r="L84" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="M84" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="M84" s="10" t="s">
-        <v>257</v>
       </c>
       <c r="N84" s="10"/>
       <c r="O84" s="10" t="s">
@@ -5696,10 +5933,10 @@
         <v>1838</v>
       </c>
       <c r="D85" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="E85" s="24" t="s">
         <v>259</v>
-      </c>
-      <c r="E85" s="24" t="s">
-        <v>260</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>106</v>
@@ -5720,10 +5957,10 @@
         <v>45533</v>
       </c>
       <c r="L85" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="M85" s="10" t="s">
         <v>261</v>
-      </c>
-      <c r="M85" s="10" t="s">
-        <v>262</v>
       </c>
       <c r="N85" s="10"/>
       <c r="O85" s="10" t="s">
@@ -5741,10 +5978,10 @@
         <v>1839</v>
       </c>
       <c r="D86" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="E86" s="24" t="s">
         <v>263</v>
-      </c>
-      <c r="E86" s="24" t="s">
-        <v>264</v>
       </c>
       <c r="F86" s="10" t="s">
         <v>18</v>
@@ -5765,10 +6002,10 @@
         <v>45533</v>
       </c>
       <c r="L86" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="M86" s="10" t="s">
         <v>265</v>
-      </c>
-      <c r="M86" s="10" t="s">
-        <v>266</v>
       </c>
       <c r="N86" s="10"/>
       <c r="O86" s="10" t="s">
@@ -5786,10 +6023,10 @@
         <v>1840</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E87" s="24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>106</v>
@@ -5810,10 +6047,10 @@
         <v>45537</v>
       </c>
       <c r="L87" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="M87" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="M87" s="10" t="s">
-        <v>257</v>
       </c>
       <c r="N87" s="10"/>
       <c r="O87" s="10" t="s">
@@ -5831,10 +6068,10 @@
         <v>1841</v>
       </c>
       <c r="D88" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="E88" s="24" t="s">
         <v>268</v>
-      </c>
-      <c r="E88" s="24" t="s">
-        <v>269</v>
       </c>
       <c r="F88" s="10" t="s">
         <v>18</v>
@@ -5855,10 +6092,10 @@
         <v>45537</v>
       </c>
       <c r="L88" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="M88" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="M88" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="N88" s="10"/>
       <c r="O88" s="10" t="s">
@@ -5876,7 +6113,7 @@
         <v>1842</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E89" s="24" t="s">
         <v>60</v>
@@ -5900,10 +6137,10 @@
         <v>45538</v>
       </c>
       <c r="L89" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="M89" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="M89" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="N89" s="10"/>
       <c r="O89" s="10" t="s">
@@ -5921,10 +6158,10 @@
         <v>1843</v>
       </c>
       <c r="D90" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="E90" s="24" t="s">
         <v>275</v>
-      </c>
-      <c r="E90" s="24" t="s">
-        <v>276</v>
       </c>
       <c r="F90" s="10" t="s">
         <v>18</v>
@@ -5945,10 +6182,10 @@
         <v>45538</v>
       </c>
       <c r="L90" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="M90" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="M90" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="N90" s="10"/>
       <c r="O90" s="10" t="s">
@@ -5966,10 +6203,10 @@
         <v>1844</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E91" s="24" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>18</v>
@@ -5990,10 +6227,10 @@
         <v>45538</v>
       </c>
       <c r="L91" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="M91" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="M91" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="N91" s="10"/>
       <c r="O91" s="10" t="s">
@@ -6011,10 +6248,10 @@
         <v>1845</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E92" s="24" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F92" s="10" t="s">
         <v>18</v>
@@ -6035,10 +6272,10 @@
         <v>45538</v>
       </c>
       <c r="L92" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="M92" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="M92" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="N92" s="10"/>
       <c r="O92" s="10" t="s">
@@ -6056,10 +6293,10 @@
         <v>1846</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E93" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>18</v>
@@ -6080,10 +6317,10 @@
         <v>45540</v>
       </c>
       <c r="L93" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="M93" s="10" t="s">
         <v>261</v>
-      </c>
-      <c r="M93" s="10" t="s">
-        <v>262</v>
       </c>
       <c r="N93" s="10"/>
       <c r="O93" s="10" t="s">
@@ -6101,10 +6338,10 @@
         <v>1847</v>
       </c>
       <c r="D94" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="E94" s="24" t="s">
         <v>282</v>
-      </c>
-      <c r="E94" s="24" t="s">
-        <v>283</v>
       </c>
       <c r="F94" s="10" t="s">
         <v>18</v>
@@ -6125,10 +6362,10 @@
         <v>45540</v>
       </c>
       <c r="L94" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="M94" s="10" t="s">
         <v>284</v>
-      </c>
-      <c r="M94" s="10" t="s">
-        <v>285</v>
       </c>
       <c r="N94" s="10"/>
       <c r="O94" s="10" t="s">
@@ -6146,10 +6383,10 @@
         <v>1848</v>
       </c>
       <c r="D95" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E95" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>106</v>
@@ -6170,10 +6407,10 @@
         <v>45540</v>
       </c>
       <c r="L95" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="M95" s="10" t="s">
         <v>284</v>
-      </c>
-      <c r="M95" s="10" t="s">
-        <v>285</v>
       </c>
       <c r="N95" s="10"/>
       <c r="O95" s="10" t="s">
@@ -6191,10 +6428,10 @@
         <v>1849</v>
       </c>
       <c r="D96" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="E96" s="24" t="s">
         <v>287</v>
-      </c>
-      <c r="E96" s="24" t="s">
-        <v>288</v>
       </c>
       <c r="F96" s="10" t="s">
         <v>106</v>
@@ -6215,10 +6452,10 @@
         <v>45541</v>
       </c>
       <c r="L96" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="M96" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="M96" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="N96" s="10"/>
       <c r="O96" s="10" t="s">
@@ -6236,7 +6473,7 @@
         <v>1850</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E97" s="24" t="s">
         <v>60</v>
@@ -6260,10 +6497,10 @@
         <v>45542</v>
       </c>
       <c r="L97" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M97" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N97" s="10"/>
       <c r="O97" s="10" t="s">
@@ -6281,16 +6518,16 @@
         <v>1851</v>
       </c>
       <c r="D98" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="E98" s="24" t="s">
         <v>293</v>
-      </c>
-      <c r="E98" s="24" t="s">
-        <v>294</v>
       </c>
       <c r="F98" s="10" t="s">
         <v>106</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H98" s="14">
         <v>42192</v>
@@ -6305,10 +6542,10 @@
         <v>45544</v>
       </c>
       <c r="L98" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="M98" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="M98" s="10" t="s">
-        <v>297</v>
       </c>
       <c r="N98" s="10"/>
       <c r="O98" s="10" t="s">
@@ -6326,16 +6563,16 @@
         <v>1852</v>
       </c>
       <c r="D99" s="23" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E99" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>18</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H99" s="14">
         <v>40635</v>
@@ -6350,10 +6587,10 @@
         <v>45544</v>
       </c>
       <c r="L99" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="M99" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="M99" s="10" t="s">
-        <v>297</v>
       </c>
       <c r="N99" s="10"/>
       <c r="O99" s="10" t="s">
@@ -6371,16 +6608,16 @@
         <v>1853</v>
       </c>
       <c r="D100" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="E100" s="24" t="s">
         <v>300</v>
-      </c>
-      <c r="E100" s="24" t="s">
-        <v>301</v>
       </c>
       <c r="F100" s="10" t="s">
         <v>106</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H100" s="14">
         <v>41640</v>
@@ -6395,10 +6632,10 @@
         <v>45544</v>
       </c>
       <c r="L100" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="M100" s="10" t="s">
         <v>302</v>
-      </c>
-      <c r="M100" s="10" t="s">
-        <v>303</v>
       </c>
       <c r="N100" s="10"/>
       <c r="O100" s="10" t="s">
@@ -6416,16 +6653,16 @@
         <v>1854</v>
       </c>
       <c r="D101" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="E101" s="24" t="s">
         <v>304</v>
-      </c>
-      <c r="E101" s="24" t="s">
-        <v>305</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>18</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H101" s="14">
         <v>43497</v>
@@ -6440,10 +6677,10 @@
         <v>45544</v>
       </c>
       <c r="L101" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="M101" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="M101" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="N101" s="10"/>
       <c r="O101" s="10" t="s">
@@ -6461,16 +6698,16 @@
         <v>1855</v>
       </c>
       <c r="D102" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E102" s="24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F102" s="10" t="s">
         <v>106</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H102" s="14">
         <v>42461</v>
@@ -6485,10 +6722,10 @@
         <v>45544</v>
       </c>
       <c r="L102" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="M102" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="M102" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="N102" s="10"/>
       <c r="O102" s="10" t="s">
@@ -6506,16 +6743,16 @@
         <v>1856</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E103" s="24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>106</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H103" s="14">
         <v>42950</v>
@@ -6530,10 +6767,10 @@
         <v>45544</v>
       </c>
       <c r="L103" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="M103" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="M103" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="N103" s="10"/>
       <c r="O103" s="10" t="s">
@@ -6551,16 +6788,16 @@
         <v>1857</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E104" s="24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F104" s="10" t="s">
         <v>106</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H104" s="14">
         <v>42070</v>
@@ -6575,10 +6812,10 @@
         <v>45544</v>
       </c>
       <c r="L104" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M104" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N104" s="10"/>
       <c r="O104" s="10" t="s">
@@ -6596,7 +6833,7 @@
         <v>1858</v>
       </c>
       <c r="D105" s="23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E105" s="24" t="s">
         <v>93</v>
@@ -6605,7 +6842,7 @@
         <v>18</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H105" s="14">
         <v>41110</v>
@@ -6641,7 +6878,7 @@
         <v>1859</v>
       </c>
       <c r="D106" s="23" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E106" s="24" t="s">
         <v>93</v>
@@ -6650,7 +6887,7 @@
         <v>18</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H106" s="14">
         <v>41640</v>
@@ -6686,7 +6923,7 @@
         <v>1860</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E107" s="24" t="s">
         <v>93</v>
@@ -6695,7 +6932,7 @@
         <v>18</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H107" s="14">
         <v>41640</v>
@@ -6731,10 +6968,10 @@
         <v>1861</v>
       </c>
       <c r="D108" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="E108" s="17" t="s">
         <v>317</v>
-      </c>
-      <c r="E108" s="17" t="s">
-        <v>318</v>
       </c>
       <c r="F108" s="10" t="s">
         <v>106</v>
@@ -6755,10 +6992,10 @@
         <v>45546</v>
       </c>
       <c r="L108" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="M108" s="10" t="s">
         <v>319</v>
-      </c>
-      <c r="M108" s="10" t="s">
-        <v>320</v>
       </c>
       <c r="N108" s="10"/>
       <c r="O108" s="10" t="s">
@@ -6776,10 +7013,10 @@
         <v>1862</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>18</v>
@@ -6800,10 +7037,10 @@
         <v>45546</v>
       </c>
       <c r="L109" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="M109" s="10" t="s">
         <v>319</v>
-      </c>
-      <c r="M109" s="10" t="s">
-        <v>320</v>
       </c>
       <c r="N109" s="10"/>
       <c r="O109" s="10" t="s">
@@ -6821,10 +7058,10 @@
         <v>1863</v>
       </c>
       <c r="D110" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="E110" s="17" t="s">
         <v>322</v>
-      </c>
-      <c r="E110" s="17" t="s">
-        <v>323</v>
       </c>
       <c r="F110" s="10" t="s">
         <v>106</v>
@@ -6845,10 +7082,10 @@
         <v>45548</v>
       </c>
       <c r="L110" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="M110" s="10" t="s">
         <v>324</v>
-      </c>
-      <c r="M110" s="10" t="s">
-        <v>325</v>
       </c>
       <c r="N110" s="10"/>
       <c r="O110" s="10" t="s">
@@ -6866,10 +7103,10 @@
         <v>1864</v>
       </c>
       <c r="D111" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="E111" s="17" t="s">
         <v>326</v>
-      </c>
-      <c r="E111" s="17" t="s">
-        <v>327</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>18</v>
@@ -6890,10 +7127,10 @@
         <v>45548</v>
       </c>
       <c r="L111" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="M111" s="10" t="s">
         <v>328</v>
-      </c>
-      <c r="M111" s="10" t="s">
-        <v>329</v>
       </c>
       <c r="N111" s="10"/>
       <c r="O111" s="10" t="s">
@@ -6911,10 +7148,10 @@
         <v>1865</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F112" s="10" t="s">
         <v>18</v>
@@ -6935,10 +7172,10 @@
         <v>45548</v>
       </c>
       <c r="L112" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="M112" s="10" t="s">
         <v>328</v>
-      </c>
-      <c r="M112" s="10" t="s">
-        <v>329</v>
       </c>
       <c r="N112" s="10"/>
       <c r="O112" s="10" t="s">
@@ -6956,7 +7193,7 @@
         <v>1866</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E113" s="17" t="s">
         <v>72</v>
@@ -6980,10 +7217,10 @@
         <v>45553</v>
       </c>
       <c r="L113" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="M113" s="10" t="s">
         <v>332</v>
-      </c>
-      <c r="M113" s="10" t="s">
-        <v>333</v>
       </c>
       <c r="N113" s="10"/>
       <c r="O113" s="10" t="s">
@@ -7001,10 +7238,10 @@
         <v>1867</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F114" s="10" t="s">
         <v>106</v>
@@ -7025,10 +7262,10 @@
         <v>45553</v>
       </c>
       <c r="L114" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="M114" s="10" t="s">
         <v>335</v>
-      </c>
-      <c r="M114" s="10" t="s">
-        <v>336</v>
       </c>
       <c r="N114" s="10"/>
       <c r="O114" s="10" t="s">
@@ -7046,10 +7283,10 @@
         <v>1868</v>
       </c>
       <c r="D115" s="16" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>106</v>
@@ -7070,10 +7307,10 @@
         <v>45553</v>
       </c>
       <c r="L115" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="M115" s="10" t="s">
         <v>324</v>
-      </c>
-      <c r="M115" s="10" t="s">
-        <v>325</v>
       </c>
       <c r="N115" s="10"/>
       <c r="O115" s="10" t="s">
@@ -7091,10 +7328,10 @@
         <v>1869</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F116" s="10" t="s">
         <v>106</v>
@@ -7115,10 +7352,10 @@
         <v>45554</v>
       </c>
       <c r="L116" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="M116" s="10" t="s">
         <v>339</v>
-      </c>
-      <c r="M116" s="10" t="s">
-        <v>340</v>
       </c>
       <c r="N116" s="10"/>
       <c r="O116" s="10" t="s">
@@ -7136,7 +7373,7 @@
         <v>1870</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E117" s="17" t="s">
         <v>61</v>
@@ -7160,10 +7397,10 @@
         <v>45554</v>
       </c>
       <c r="L117" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="M117" s="10" t="s">
         <v>342</v>
-      </c>
-      <c r="M117" s="10" t="s">
-        <v>343</v>
       </c>
       <c r="N117" s="10"/>
       <c r="O117" s="10" t="s">
@@ -7181,10 +7418,10 @@
         <v>1871</v>
       </c>
       <c r="D118" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="E118" s="17" t="s">
         <v>344</v>
-      </c>
-      <c r="E118" s="17" t="s">
-        <v>345</v>
       </c>
       <c r="F118" s="10" t="s">
         <v>106</v>
@@ -7205,10 +7442,10 @@
         <v>45554</v>
       </c>
       <c r="L118" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="M118" s="10" t="s">
         <v>346</v>
-      </c>
-      <c r="M118" s="10" t="s">
-        <v>347</v>
       </c>
       <c r="N118" s="10"/>
       <c r="O118" s="10" t="s">
@@ -7229,7 +7466,7 @@
         <v>135</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>106</v>
@@ -7250,10 +7487,10 @@
         <v>45554</v>
       </c>
       <c r="L119" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="M119" s="10" t="s">
         <v>346</v>
-      </c>
-      <c r="M119" s="10" t="s">
-        <v>347</v>
       </c>
       <c r="N119" s="10"/>
       <c r="O119" s="10" t="s">
@@ -7271,10 +7508,10 @@
         <v>1873</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F120" s="10" t="s">
         <v>106</v>
@@ -7295,10 +7532,10 @@
         <v>45555</v>
       </c>
       <c r="L120" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="M120" s="10" t="s">
         <v>319</v>
-      </c>
-      <c r="M120" s="10" t="s">
-        <v>320</v>
       </c>
       <c r="N120" s="10"/>
       <c r="O120" s="10" t="s">
@@ -7316,10 +7553,10 @@
         <v>1874</v>
       </c>
       <c r="D121" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="E121" s="17" t="s">
         <v>349</v>
-      </c>
-      <c r="E121" s="17" t="s">
-        <v>350</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>106</v>
@@ -7340,10 +7577,10 @@
         <v>45556</v>
       </c>
       <c r="L121" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="M121" s="10" t="s">
         <v>351</v>
-      </c>
-      <c r="M121" s="10" t="s">
-        <v>352</v>
       </c>
       <c r="N121" s="10"/>
       <c r="O121" s="10" t="s">
@@ -7361,10 +7598,10 @@
         <v>1875</v>
       </c>
       <c r="D122" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="E122" s="17" t="s">
         <v>353</v>
-      </c>
-      <c r="E122" s="17" t="s">
-        <v>354</v>
       </c>
       <c r="F122" s="10" t="s">
         <v>106</v>
@@ -7385,10 +7622,10 @@
         <v>45559</v>
       </c>
       <c r="L122" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M122" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N122" s="10"/>
       <c r="O122" s="10" t="s">
@@ -7406,10 +7643,10 @@
         <v>1876</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>18</v>
@@ -7430,10 +7667,10 @@
         <v>45559</v>
       </c>
       <c r="L123" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M123" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N123" s="10"/>
       <c r="O123" s="10" t="s">
@@ -7451,10 +7688,10 @@
         <v>1877</v>
       </c>
       <c r="D124" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="E124" s="17" t="s">
         <v>360</v>
-      </c>
-      <c r="E124" s="17" t="s">
-        <v>361</v>
       </c>
       <c r="F124" s="10" t="s">
         <v>106</v>
@@ -7475,10 +7712,10 @@
         <v>45560</v>
       </c>
       <c r="L124" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="M124" s="10" t="s">
         <v>362</v>
-      </c>
-      <c r="M124" s="10" t="s">
-        <v>363</v>
       </c>
       <c r="N124" s="10"/>
       <c r="O124" s="10" t="s">
@@ -7496,10 +7733,10 @@
         <v>1878</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>106</v>
@@ -7520,10 +7757,10 @@
         <v>45560</v>
       </c>
       <c r="L125" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="M125" s="10" t="s">
         <v>362</v>
-      </c>
-      <c r="M125" s="10" t="s">
-        <v>363</v>
       </c>
       <c r="N125" s="10"/>
       <c r="O125" s="10" t="s">
@@ -7540,25 +7777,39 @@
       <c r="C126" s="15">
         <v>1879</v>
       </c>
-      <c r="D126" s="16"/>
-      <c r="E126" s="17"/>
-      <c r="F126" s="10"/>
+      <c r="D126" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="E126" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G126" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H126" s="14"/>
+      <c r="H126" s="14">
+        <v>42766</v>
+      </c>
       <c r="I126" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J126" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K126" s="14"/>
-      <c r="L126" s="10"/>
-      <c r="M126" s="10"/>
+      <c r="K126" s="14">
+        <v>45560</v>
+      </c>
+      <c r="L126" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="M126" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="N126" s="10"/>
       <c r="O126" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="127" spans="1:15" s="5" customFormat="1">
@@ -7571,25 +7822,39 @@
       <c r="C127" s="11">
         <v>1880</v>
       </c>
-      <c r="D127" s="16"/>
-      <c r="E127" s="17"/>
-      <c r="F127" s="10"/>
+      <c r="D127" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="E127" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="F127" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G127" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H127" s="14"/>
+      <c r="H127" s="14">
+        <v>43327</v>
+      </c>
       <c r="I127" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J127" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K127" s="14"/>
-      <c r="L127" s="10"/>
-      <c r="M127" s="10"/>
+      <c r="K127" s="14">
+        <v>45560</v>
+      </c>
+      <c r="L127" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="M127" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="N127" s="10"/>
       <c r="O127" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="128" spans="1:15" s="5" customFormat="1">
@@ -7602,25 +7867,39 @@
       <c r="C128" s="15">
         <v>1881</v>
       </c>
-      <c r="D128" s="16"/>
-      <c r="E128" s="17"/>
-      <c r="F128" s="10"/>
+      <c r="D128" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="E128" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="F128" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G128" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H128" s="14"/>
+      <c r="H128" s="14">
+        <v>42397</v>
+      </c>
       <c r="I128" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J128" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K128" s="14"/>
-      <c r="L128" s="10"/>
-      <c r="M128" s="10"/>
+      <c r="K128" s="14">
+        <v>45560</v>
+      </c>
+      <c r="L128" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="M128" s="10" t="s">
+        <v>373</v>
+      </c>
       <c r="N128" s="10"/>
       <c r="O128" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129" spans="1:15" s="5" customFormat="1">
@@ -7633,25 +7912,39 @@
       <c r="C129" s="11">
         <v>1882</v>
       </c>
-      <c r="D129" s="16"/>
-      <c r="E129" s="17"/>
-      <c r="F129" s="10"/>
+      <c r="D129" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="E129" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="F129" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G129" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H129" s="14"/>
+      <c r="H129" s="14">
+        <v>43422</v>
+      </c>
       <c r="I129" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J129" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K129" s="14"/>
-      <c r="L129" s="10"/>
-      <c r="M129" s="10"/>
+      <c r="K129" s="14">
+        <v>45560</v>
+      </c>
+      <c r="L129" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="M129" s="10" t="s">
+        <v>373</v>
+      </c>
       <c r="N129" s="10"/>
       <c r="O129" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="130" spans="1:15" s="5" customFormat="1">
@@ -7664,25 +7957,39 @@
       <c r="C130" s="15">
         <v>1883</v>
       </c>
-      <c r="D130" s="16"/>
-      <c r="E130" s="17"/>
-      <c r="F130" s="10"/>
+      <c r="D130" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="E130" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="F130" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G130" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H130" s="14"/>
+      <c r="H130" s="14">
+        <v>43692</v>
+      </c>
       <c r="I130" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J130" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K130" s="14"/>
-      <c r="L130" s="10"/>
-      <c r="M130" s="10"/>
+      <c r="K130" s="14">
+        <v>41923</v>
+      </c>
+      <c r="L130" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="M130" s="10" t="s">
+        <v>378</v>
+      </c>
       <c r="N130" s="10"/>
       <c r="O130" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="131" spans="1:15" s="5" customFormat="1">
@@ -7695,25 +8002,39 @@
       <c r="C131" s="11">
         <v>1884</v>
       </c>
-      <c r="D131" s="16"/>
-      <c r="E131" s="24"/>
-      <c r="F131" s="10"/>
+      <c r="D131" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E131" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="F131" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G131" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H131" s="14"/>
+        <v>298</v>
+      </c>
+      <c r="H131" s="14">
+        <v>41835</v>
+      </c>
       <c r="I131" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J131" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K131" s="14"/>
-      <c r="L131" s="10"/>
-      <c r="M131" s="10"/>
+      <c r="K131" s="14">
+        <v>41923</v>
+      </c>
+      <c r="L131" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="M131" s="10" t="s">
+        <v>378</v>
+      </c>
       <c r="N131" s="10"/>
       <c r="O131" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="132" spans="1:15" s="5" customFormat="1">
@@ -7726,25 +8047,39 @@
       <c r="C132" s="15">
         <v>1885</v>
       </c>
-      <c r="D132" s="16"/>
-      <c r="E132" s="17"/>
-      <c r="F132" s="10"/>
+      <c r="D132" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="E132" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="F132" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G132" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H132" s="14"/>
+      <c r="H132" s="14">
+        <v>42592</v>
+      </c>
       <c r="I132" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J132" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K132" s="14"/>
-      <c r="L132" s="10"/>
-      <c r="M132" s="10"/>
+      <c r="K132" s="14">
+        <v>41923</v>
+      </c>
+      <c r="L132" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="M132" s="10" t="s">
+        <v>383</v>
+      </c>
       <c r="N132" s="10"/>
       <c r="O132" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="133" spans="1:15" s="5" customFormat="1">
@@ -7757,25 +8092,39 @@
       <c r="C133" s="11">
         <v>1886</v>
       </c>
-      <c r="D133" s="16"/>
-      <c r="E133" s="17"/>
-      <c r="F133" s="10"/>
+      <c r="D133" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="E133" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="F133" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G133" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H133" s="14"/>
+      <c r="H133" s="14">
+        <v>42983</v>
+      </c>
       <c r="I133" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J133" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K133" s="14"/>
-      <c r="L133" s="10"/>
-      <c r="M133" s="10"/>
+      <c r="K133" s="14">
+        <v>41923</v>
+      </c>
+      <c r="L133" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="M133" s="10" t="s">
+        <v>383</v>
+      </c>
       <c r="N133" s="10"/>
       <c r="O133" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="134" spans="1:15" s="5" customFormat="1">
@@ -7788,22 +8137,36 @@
       <c r="C134" s="15">
         <v>1887</v>
       </c>
-      <c r="D134" s="16"/>
-      <c r="E134" s="17"/>
-      <c r="F134" s="10"/>
+      <c r="D134" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="E134" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="F134" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G134" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H134" s="14"/>
+      <c r="H134" s="14">
+        <v>43296</v>
+      </c>
       <c r="I134" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J134" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K134" s="14"/>
-      <c r="L134" s="10"/>
-      <c r="M134" s="10"/>
+      <c r="K134" s="14">
+        <v>41923</v>
+      </c>
+      <c r="L134" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="M134" s="10" t="s">
+        <v>387</v>
+      </c>
       <c r="N134" s="10"/>
       <c r="O134" s="10" t="s">
         <v>24</v>
@@ -7819,22 +8182,36 @@
       <c r="C135" s="11">
         <v>1888</v>
       </c>
-      <c r="D135" s="16"/>
-      <c r="E135" s="17"/>
-      <c r="F135" s="10"/>
+      <c r="D135" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="E135" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="F135" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G135" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H135" s="14"/>
+      <c r="H135" s="14">
+        <v>42596</v>
+      </c>
       <c r="I135" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J135" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K135" s="14"/>
-      <c r="L135" s="10"/>
-      <c r="M135" s="10"/>
+      <c r="K135" s="14">
+        <v>41923</v>
+      </c>
+      <c r="L135" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="M135" s="10" t="s">
+        <v>391</v>
+      </c>
       <c r="N135" s="10"/>
       <c r="O135" s="10" t="s">
         <v>24</v>
@@ -7850,25 +8227,39 @@
       <c r="C136" s="15">
         <v>1889</v>
       </c>
-      <c r="D136" s="16"/>
-      <c r="E136" s="17"/>
-      <c r="F136" s="10"/>
+      <c r="D136" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="E136" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="F136" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G136" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H136" s="14"/>
+      <c r="H136" s="14">
+        <v>43233</v>
+      </c>
       <c r="I136" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J136" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K136" s="14"/>
-      <c r="L136" s="10"/>
-      <c r="M136" s="10"/>
+      <c r="K136" s="14">
+        <v>45576</v>
+      </c>
+      <c r="L136" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="M136" s="10" t="s">
+        <v>395</v>
+      </c>
       <c r="N136" s="10"/>
       <c r="O136" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="137" spans="1:15" s="5" customFormat="1">
@@ -7881,25 +8272,39 @@
       <c r="C137" s="11">
         <v>1890</v>
       </c>
-      <c r="D137" s="16"/>
-      <c r="E137" s="17"/>
-      <c r="F137" s="10"/>
+      <c r="D137" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="E137" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="F137" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G137" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H137" s="14"/>
+      <c r="H137" s="14">
+        <v>42796</v>
+      </c>
       <c r="I137" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J137" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K137" s="14"/>
-      <c r="L137" s="10"/>
-      <c r="M137" s="10"/>
+      <c r="K137" s="14">
+        <v>45576</v>
+      </c>
+      <c r="L137" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="M137" s="10" t="s">
+        <v>395</v>
+      </c>
       <c r="N137" s="10"/>
       <c r="O137" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="138" spans="1:15" s="5" customFormat="1">
@@ -7912,25 +8317,39 @@
       <c r="C138" s="15">
         <v>1891</v>
       </c>
-      <c r="D138" s="16"/>
-      <c r="E138" s="17"/>
-      <c r="F138" s="10"/>
+      <c r="D138" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="E138" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="F138" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G138" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H138" s="14"/>
+      <c r="H138" s="14">
+        <v>43661</v>
+      </c>
       <c r="I138" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J138" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K138" s="14"/>
-      <c r="L138" s="10"/>
-      <c r="M138" s="10"/>
+      <c r="K138" s="14">
+        <v>45576</v>
+      </c>
+      <c r="L138" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="M138" s="10" t="s">
+        <v>383</v>
+      </c>
       <c r="N138" s="10"/>
       <c r="O138" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="139" spans="1:15" s="5" customFormat="1">
@@ -7943,25 +8362,39 @@
       <c r="C139" s="11">
         <v>1892</v>
       </c>
-      <c r="D139" s="16"/>
-      <c r="E139" s="17"/>
-      <c r="F139" s="10"/>
+      <c r="D139" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="E139" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="F139" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G139" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H139" s="14"/>
+      <c r="H139" s="14">
+        <v>42531</v>
+      </c>
       <c r="I139" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J139" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K139" s="14"/>
-      <c r="L139" s="10"/>
-      <c r="M139" s="10"/>
+      <c r="K139" s="14">
+        <v>45576</v>
+      </c>
+      <c r="L139" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="M139" s="10" t="s">
+        <v>402</v>
+      </c>
       <c r="N139" s="10"/>
       <c r="O139" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="140" spans="1:15" s="5" customFormat="1">
@@ -7974,25 +8407,39 @@
       <c r="C140" s="15">
         <v>1893</v>
       </c>
-      <c r="D140" s="12"/>
-      <c r="E140" s="13"/>
-      <c r="F140" s="10"/>
+      <c r="D140" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="E140" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="F140" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G140" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H140" s="14"/>
+      <c r="H140" s="14">
+        <v>42840</v>
+      </c>
       <c r="I140" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J140" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K140" s="14"/>
-      <c r="L140" s="10"/>
-      <c r="M140" s="10"/>
+      <c r="K140" s="14">
+        <v>45576</v>
+      </c>
+      <c r="L140" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="M140" s="10" t="s">
+        <v>402</v>
+      </c>
       <c r="N140" s="10"/>
       <c r="O140" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="141" spans="1:15" s="5" customFormat="1">
@@ -8005,25 +8452,39 @@
       <c r="C141" s="11">
         <v>1894</v>
       </c>
-      <c r="D141" s="16"/>
-      <c r="E141" s="17"/>
-      <c r="F141" s="10"/>
+      <c r="D141" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E141" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="F141" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G141" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H141" s="14"/>
+      <c r="H141" s="14">
+        <v>43317</v>
+      </c>
       <c r="I141" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J141" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K141" s="14"/>
-      <c r="L141" s="10"/>
-      <c r="M141" s="10"/>
+      <c r="K141" s="14">
+        <v>45576</v>
+      </c>
+      <c r="L141" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="M141" s="10" t="s">
+        <v>402</v>
+      </c>
       <c r="N141" s="10"/>
       <c r="O141" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142" spans="1:15" s="5" customFormat="1">
@@ -8036,25 +8497,39 @@
       <c r="C142" s="15">
         <v>1895</v>
       </c>
-      <c r="D142" s="16"/>
-      <c r="E142" s="17"/>
-      <c r="F142" s="10"/>
+      <c r="D142" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="E142" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F142" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G142" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H142" s="14"/>
+      <c r="H142" s="14">
+        <v>41861</v>
+      </c>
       <c r="I142" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J142" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K142" s="14"/>
-      <c r="L142" s="10"/>
-      <c r="M142" s="10"/>
+      <c r="K142" s="14">
+        <v>45577</v>
+      </c>
+      <c r="L142" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="M142" s="10" t="s">
+        <v>408</v>
+      </c>
       <c r="N142" s="10"/>
       <c r="O142" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="143" spans="1:15" s="5" customFormat="1">
@@ -8067,25 +8542,39 @@
       <c r="C143" s="11">
         <v>1896</v>
       </c>
-      <c r="D143" s="16"/>
-      <c r="E143" s="17"/>
-      <c r="F143" s="10"/>
+      <c r="D143" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="E143" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F143" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G143" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H143" s="14"/>
+      <c r="H143" s="14">
+        <v>41069</v>
+      </c>
       <c r="I143" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J143" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K143" s="14"/>
-      <c r="L143" s="10"/>
-      <c r="M143" s="10"/>
+      <c r="K143" s="14">
+        <v>45577</v>
+      </c>
+      <c r="L143" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="M143" s="10" t="s">
+        <v>408</v>
+      </c>
       <c r="N143" s="10"/>
       <c r="O143" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="144" spans="1:15" s="5" customFormat="1">
@@ -8098,22 +8587,36 @@
       <c r="C144" s="15">
         <v>1897</v>
       </c>
-      <c r="D144" s="16"/>
-      <c r="E144" s="17"/>
-      <c r="F144" s="10"/>
+      <c r="D144" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="E144" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="F144" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G144" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H144" s="14"/>
+      <c r="H144" s="14">
+        <v>43231</v>
+      </c>
       <c r="I144" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J144" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K144" s="14"/>
-      <c r="L144" s="10"/>
-      <c r="M144" s="10"/>
+      <c r="K144" s="14">
+        <v>45577</v>
+      </c>
+      <c r="L144" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="M144" s="10" t="s">
+        <v>413</v>
+      </c>
       <c r="N144" s="10"/>
       <c r="O144" s="10" t="s">
         <v>24</v>
@@ -8129,22 +8632,36 @@
       <c r="C145" s="11">
         <v>1898</v>
       </c>
-      <c r="D145" s="16"/>
-      <c r="E145" s="17"/>
-      <c r="F145" s="10"/>
+      <c r="D145" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="E145" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="F145" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G145" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H145" s="14"/>
+      <c r="H145" s="14">
+        <v>43150</v>
+      </c>
       <c r="I145" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J145" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K145" s="14"/>
-      <c r="L145" s="10"/>
-      <c r="M145" s="10"/>
+      <c r="K145" s="14">
+        <v>45577</v>
+      </c>
+      <c r="L145" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="M145" s="10" t="s">
+        <v>417</v>
+      </c>
       <c r="N145" s="10"/>
       <c r="O145" s="10" t="s">
         <v>24</v>
@@ -8160,25 +8677,39 @@
       <c r="C146" s="15">
         <v>1899</v>
       </c>
-      <c r="D146" s="16"/>
-      <c r="E146" s="17"/>
-      <c r="F146" s="10"/>
+      <c r="D146" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="E146" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="F146" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G146" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H146" s="14"/>
+      <c r="H146" s="14">
+        <v>42845</v>
+      </c>
       <c r="I146" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J146" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K146" s="14"/>
-      <c r="L146" s="10"/>
-      <c r="M146" s="10"/>
+      <c r="K146" s="14">
+        <v>45577</v>
+      </c>
+      <c r="L146" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="M146" s="10" t="s">
+        <v>421</v>
+      </c>
       <c r="N146" s="10"/>
       <c r="O146" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="147" spans="1:15" s="5" customFormat="1">
@@ -8191,25 +8722,39 @@
       <c r="C147" s="11">
         <v>1900</v>
       </c>
-      <c r="D147" s="16"/>
-      <c r="E147" s="17"/>
-      <c r="F147" s="10"/>
+      <c r="D147" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="E147" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="F147" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G147" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H147" s="14"/>
+      <c r="H147" s="14">
+        <v>43221</v>
+      </c>
       <c r="I147" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J147" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K147" s="14"/>
-      <c r="L147" s="10"/>
-      <c r="M147" s="10"/>
+      <c r="K147" s="14">
+        <v>45577</v>
+      </c>
+      <c r="L147" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="M147" s="10" t="s">
+        <v>421</v>
+      </c>
       <c r="N147" s="10"/>
       <c r="O147" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="148" spans="1:15" s="5" customFormat="1">
@@ -8222,25 +8767,39 @@
       <c r="C148" s="15">
         <v>1901</v>
       </c>
-      <c r="D148" s="16"/>
-      <c r="E148" s="17"/>
-      <c r="F148" s="10"/>
+      <c r="D148" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="E148" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="F148" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G148" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H148" s="14"/>
+      <c r="H148" s="14">
+        <v>43479</v>
+      </c>
       <c r="I148" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J148" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K148" s="14"/>
-      <c r="L148" s="10"/>
-      <c r="M148" s="10"/>
+      <c r="K148" s="14">
+        <v>45577</v>
+      </c>
+      <c r="L148" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="M148" s="10" t="s">
+        <v>426</v>
+      </c>
       <c r="N148" s="10"/>
       <c r="O148" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="149" spans="1:15" s="5" customFormat="1">
@@ -8253,25 +8812,39 @@
       <c r="C149" s="11">
         <v>1902</v>
       </c>
-      <c r="D149" s="16"/>
-      <c r="E149" s="17"/>
-      <c r="F149" s="10"/>
+      <c r="D149" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="E149" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="F149" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G149" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H149" s="14"/>
+      <c r="H149" s="14">
+        <v>41709</v>
+      </c>
       <c r="I149" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J149" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K149" s="14"/>
-      <c r="L149" s="10"/>
-      <c r="M149" s="10"/>
+      <c r="K149" s="14">
+        <v>45577</v>
+      </c>
+      <c r="L149" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="M149" s="10" t="s">
+        <v>426</v>
+      </c>
       <c r="N149" s="10"/>
       <c r="O149" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="150" spans="1:15" s="5" customFormat="1">
@@ -8284,22 +8857,36 @@
       <c r="C150" s="15">
         <v>1903</v>
       </c>
-      <c r="D150" s="16"/>
-      <c r="E150" s="17"/>
-      <c r="F150" s="10"/>
+      <c r="D150" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="E150" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="F150" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G150" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H150" s="14"/>
+      <c r="H150" s="14">
+        <v>43672</v>
+      </c>
       <c r="I150" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J150" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K150" s="14"/>
-      <c r="L150" s="10"/>
-      <c r="M150" s="10"/>
+      <c r="K150" s="14">
+        <v>45577</v>
+      </c>
+      <c r="L150" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="M150" s="10" t="s">
+        <v>431</v>
+      </c>
       <c r="N150" s="10"/>
       <c r="O150" s="10" t="s">
         <v>24</v>
@@ -8315,22 +8902,36 @@
       <c r="C151" s="11">
         <v>1904</v>
       </c>
-      <c r="D151" s="16"/>
-      <c r="E151" s="17"/>
-      <c r="F151" s="10"/>
+      <c r="D151" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E151" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="F151" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="G151" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H151" s="14"/>
+      <c r="H151" s="14">
+        <v>43466</v>
+      </c>
       <c r="I151" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J151" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K151" s="14"/>
-      <c r="L151" s="10"/>
-      <c r="M151" s="10"/>
+      <c r="K151" s="14">
+        <v>45577</v>
+      </c>
+      <c r="L151" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="M151" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="N151" s="10"/>
       <c r="O151" s="10" t="s">
         <v>24</v>
@@ -8346,22 +8947,36 @@
       <c r="C152" s="15">
         <v>1905</v>
       </c>
-      <c r="D152" s="16"/>
-      <c r="E152" s="17"/>
-      <c r="F152" s="10"/>
+      <c r="D152" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="E152" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F152" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="G152" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H152" s="14"/>
+      <c r="H152" s="14">
+        <v>43466</v>
+      </c>
       <c r="I152" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J152" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K152" s="14"/>
-      <c r="L152" s="10"/>
-      <c r="M152" s="10"/>
+      <c r="K152" s="14">
+        <v>45577</v>
+      </c>
+      <c r="L152" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="M152" s="10" t="s">
+        <v>438</v>
+      </c>
       <c r="N152" s="10"/>
       <c r="O152" s="10" t="s">
         <v>24</v>
@@ -12036,29 +12651,29 @@
     <row r="1" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1"/>
     <row r="2" spans="1:2" s="2" customFormat="1" ht="21">
       <c r="A2" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTIF('All Record'!$F:$F,"Female")</f>
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="21">
       <c r="A3" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B3" s="3">
         <f>COUNTIF('All Record'!$F:$F,"Male")</f>
-        <v>68</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="21">
       <c r="A4" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B4" s="3">
         <f>B2+B3</f>
-        <v>123</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
